--- a/Result/profitability/2114.xlsx
+++ b/Result/profitability/2114.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2875</v>
+        <v>1.33</v>
       </c>
       <c r="N2" t="n">
-        <v>37.69750000000001</v>
+        <v>37.4325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1875</v>
+        <v>1.22875</v>
       </c>
       <c r="N3" t="n">
-        <v>34.96</v>
+        <v>34.57125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.61</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0975</v>
+        <v>1.12375</v>
       </c>
       <c r="N4" t="n">
-        <v>31.88875</v>
+        <v>31.65125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02875</v>
+        <v>1.0925</v>
       </c>
       <c r="N5" t="n">
-        <v>29.38375</v>
+        <v>29.07375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.54</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9524999999999999</v>
+        <v>0.9662499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>26.91125</v>
+        <v>26.7475</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8487499999999999</v>
+        <v>0.85125</v>
       </c>
       <c r="N7" t="n">
-        <v>24.8175</v>
+        <v>24.68125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.89</v>
       </c>
       <c r="M8" t="n">
-        <v>0.755</v>
+        <v>0.78625</v>
       </c>
       <c r="N8" t="n">
-        <v>23.2775</v>
+        <v>23.00125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.92</v>
       </c>
       <c r="M9" t="n">
-        <v>0.69375</v>
+        <v>0.6937500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>21.05875</v>
@@ -1899,7 +1899,7 @@
         <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>0.78875</v>
+        <v>0.7887500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>22.26375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>421</v>
+      </c>
+      <c r="D75" t="n">
+        <v>261</v>
+      </c>
+      <c r="E75" t="n">
+        <v>160</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="G75" t="n">
+        <v>130</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>27</v>
+      </c>
+      <c r="J75" t="n">
+        <v>157</v>
+      </c>
+      <c r="K75" t="n">
+        <v>130</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.43875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.83750000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.177304964539007</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.210000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05487956295008689</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4434782608695653</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.479999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06117414898865314</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
